--- a/artfynd/A 48348-2024 artfynd.xlsx
+++ b/artfynd/A 48348-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111026118</v>
       </c>
       <c r="B2" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,14 +707,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsen (Åsen), Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437411.7210614016</v>
+        <v>437412</v>
       </c>
       <c r="R2" t="n">
-        <v>6751647.214307335</v>
+        <v>6751647</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111440369</v>
+        <v>111440239</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,35 +798,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oradtjärnen (Oradtjärnen), Dlr</t>
+          <t>Oradtjärnen, Oradtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436835.7738989469</v>
+        <v>436891</v>
       </c>
       <c r="R3" t="n">
-        <v>6751667.128594172</v>
+        <v>6751465</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111440239</v>
+        <v>118348358</v>
       </c>
       <c r="B4" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,20 +924,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Oradtjärnen (Oradtjärnen), Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436891.1769261181</v>
+        <v>436819</v>
       </c>
       <c r="R4" t="n">
-        <v>6751464.610090013</v>
+        <v>6751894</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,22 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,15 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111440259</v>
+        <v>118348359</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,38 +1003,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oradtjärnen (Oradtjärnen), Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436890.23657991</v>
+        <v>436902</v>
       </c>
       <c r="R5" t="n">
-        <v>6751466.574024525</v>
+        <v>6751965</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1057,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111440359</v>
+        <v>118348360</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,38 +1100,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oradtjärnen (Oradtjärnen), Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436843.062775769</v>
+        <v>437004</v>
       </c>
       <c r="R6" t="n">
-        <v>6751638.278664739</v>
+        <v>6751977</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,22 +1154,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,15 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111440236</v>
+        <v>118348361</v>
       </c>
       <c r="B7" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,38 +1197,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oradtjärnen (Oradtjärnen), Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436891.1769261181</v>
+        <v>437101</v>
       </c>
       <c r="R7" t="n">
-        <v>6751464.610090013</v>
+        <v>6752037</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1251,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,15 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111440954</v>
+        <v>118348362</v>
       </c>
       <c r="B8" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,43 +1294,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åsen (Åsen), Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437016</v>
+        <v>437172</v>
       </c>
       <c r="R8" t="n">
-        <v>6751564</v>
+        <v>6752035</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,22 +1348,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,15 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111440929</v>
+        <v>118348363</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,38 +1391,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsen (Åsen), Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437016</v>
+        <v>437196</v>
       </c>
       <c r="R9" t="n">
-        <v>6751564</v>
+        <v>6751964</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,22 +1445,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,15 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118348362</v>
+        <v>121448548</v>
       </c>
       <c r="B10" t="n">
-        <v>78136</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437172</v>
+        <v>437511</v>
       </c>
       <c r="R10" t="n">
-        <v>6752035</v>
+        <v>6751768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,15 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118348360</v>
+        <v>121448841</v>
       </c>
       <c r="B11" t="n">
-        <v>78136</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,14 +1605,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437004</v>
+        <v>437073</v>
       </c>
       <c r="R11" t="n">
-        <v>6751977</v>
+        <v>6751772</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,12 +1639,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,15 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118348346</v>
+        <v>111441110</v>
       </c>
       <c r="B12" t="n">
-        <v>74603</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,37 +1692,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436906</v>
+        <v>437072</v>
       </c>
       <c r="R12" t="n">
-        <v>6751733</v>
+        <v>6751515</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,12 +1747,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,15 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118348348</v>
+        <v>118348352</v>
       </c>
       <c r="B13" t="n">
-        <v>79080</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1800,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436896</v>
+        <v>437425</v>
       </c>
       <c r="R13" t="n">
-        <v>6751461</v>
+        <v>6751657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,15 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118348495</v>
+        <v>121448545</v>
       </c>
       <c r="B14" t="n">
-        <v>91412</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,37 +1897,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stamsmyren, Venjan, Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>437117</v>
+        <v>437437</v>
       </c>
       <c r="R14" t="n">
-        <v>6751889</v>
+        <v>6751682</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,22 +1951,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,15 +1983,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118348350</v>
+        <v>121448547</v>
       </c>
       <c r="B15" t="n">
-        <v>79080</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,21 +1994,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2148,10 +2018,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437350</v>
+        <v>437429</v>
       </c>
       <c r="R15" t="n">
-        <v>6751659</v>
+        <v>6751670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,15 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118348358</v>
+        <v>118348495</v>
       </c>
       <c r="B16" t="n">
-        <v>78136</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,37 +2091,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436819</v>
+        <v>437117</v>
       </c>
       <c r="R16" t="n">
-        <v>6751894</v>
+        <v>6751889</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,12 +2145,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,15 +2187,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118348354</v>
+        <v>118348351</v>
       </c>
       <c r="B17" t="n">
-        <v>78491</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,21 +2198,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2352,10 +2222,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436884</v>
+        <v>437246</v>
       </c>
       <c r="R17" t="n">
-        <v>6751478</v>
+        <v>6751600</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2414,15 +2284,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118348355</v>
+        <v>121448787</v>
       </c>
       <c r="B18" t="n">
-        <v>78491</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,34 +2295,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436822</v>
+        <v>437024</v>
       </c>
       <c r="R18" t="n">
-        <v>6751849</v>
+        <v>6751557</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,12 +2349,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,50 +2391,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118348361</v>
+        <v>121448827</v>
       </c>
       <c r="B19" t="n">
-        <v>78136</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437101</v>
+        <v>436923</v>
       </c>
       <c r="R19" t="n">
-        <v>6752037</v>
+        <v>6751806</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,12 +2456,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,53 +2498,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118348363</v>
+        <v>111440259</v>
       </c>
       <c r="B20" t="n">
-        <v>78136</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Oradtjärnen, Oradtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437196</v>
+        <v>436890</v>
       </c>
       <c r="R20" t="n">
-        <v>6751964</v>
+        <v>6751467</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2688,12 +2564,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,53 +2606,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118348351</v>
+        <v>111440359</v>
       </c>
       <c r="B21" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Oradtjärnen, Oradtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437246</v>
+        <v>436843</v>
       </c>
       <c r="R21" t="n">
-        <v>6751600</v>
+        <v>6751638</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2790,12 +2672,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,53 +2714,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118348352</v>
+        <v>111440369</v>
       </c>
       <c r="B22" t="n">
-        <v>91798</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Oradtjärnen, Oradtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437425</v>
+        <v>436835</v>
       </c>
       <c r="R22" t="n">
-        <v>6751657</v>
+        <v>6751667</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2892,12 +2780,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,53 +2822,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118348347</v>
+        <v>111440929</v>
       </c>
       <c r="B23" t="n">
-        <v>79109</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437246</v>
+        <v>437016</v>
       </c>
       <c r="R23" t="n">
-        <v>6751611</v>
+        <v>6751564</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2994,12 +2888,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3026,58 +2930,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121448863</v>
+        <v>111441133</v>
       </c>
       <c r="B24" t="n">
-        <v>78352</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437149</v>
+        <v>437072</v>
       </c>
       <c r="R24" t="n">
-        <v>6751833</v>
+        <v>6751515</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3101,22 +2996,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,50 +3038,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121448843</v>
+        <v>118348354</v>
       </c>
       <c r="B25" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437149</v>
+        <v>436884</v>
       </c>
       <c r="R25" t="n">
-        <v>6751802</v>
+        <v>6751478</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,22 +3103,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3255,19 +3135,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121448790</v>
+        <v>118348355</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3291,14 +3166,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åsen, Åsen, Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437024</v>
+        <v>436822</v>
       </c>
       <c r="R26" t="n">
-        <v>6751557</v>
+        <v>6751849</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,22 +3200,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3367,19 +3232,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121448794</v>
+        <v>121448546</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3403,14 +3263,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åsen, Åsen, Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436844</v>
+        <v>437496</v>
       </c>
       <c r="R27" t="n">
-        <v>6751622</v>
+        <v>6751751</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,22 +3297,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,19 +3329,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121448795</v>
+        <v>121448724</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3519,10 +3364,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436891</v>
+        <v>437053</v>
       </c>
       <c r="R28" t="n">
-        <v>6751714</v>
+        <v>6751494</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3554,7 +3399,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3564,7 +3409,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,37 +3436,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121448787</v>
+        <v>121448783</v>
       </c>
       <c r="B29" t="n">
-        <v>90748</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3631,10 +3471,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437024</v>
+        <v>437008</v>
       </c>
       <c r="R29" t="n">
-        <v>6751557</v>
+        <v>6751526</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3666,7 +3506,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3676,7 +3516,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3703,19 +3543,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121448800</v>
+        <v>121448790</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3743,10 +3578,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436862</v>
+        <v>437024</v>
       </c>
       <c r="R30" t="n">
-        <v>6751745</v>
+        <v>6751557</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3613,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3788,7 +3623,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3815,19 +3650,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121448822</v>
+        <v>121448792</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3855,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436909</v>
+        <v>437009</v>
       </c>
       <c r="R31" t="n">
-        <v>6751837</v>
+        <v>6751557</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3890,7 +3720,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3900,7 +3730,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,50 +3757,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121448545</v>
+        <v>121448794</v>
       </c>
       <c r="B32" t="n">
-        <v>92016</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>437437</v>
+        <v>436844</v>
       </c>
       <c r="R32" t="n">
-        <v>6751682</v>
+        <v>6751622</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3997,12 +3822,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,37 +3864,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121448819</v>
+        <v>121448795</v>
       </c>
       <c r="B33" t="n">
-        <v>78353</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4069,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436864</v>
+        <v>436891</v>
       </c>
       <c r="R33" t="n">
-        <v>6751900</v>
+        <v>6751714</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4104,7 +3934,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4114,7 +3944,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,19 +3971,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121448809</v>
+        <v>121448800</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4181,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436818</v>
+        <v>436862</v>
       </c>
       <c r="R34" t="n">
-        <v>6751839</v>
+        <v>6751745</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4216,7 +4041,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4226,7 +4051,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,50 +4078,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121448547</v>
+        <v>121448809</v>
       </c>
       <c r="B35" t="n">
-        <v>92016</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>437429</v>
+        <v>436818</v>
       </c>
       <c r="R35" t="n">
-        <v>6751670</v>
+        <v>6751839</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4323,12 +4143,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4355,19 +4185,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121448792</v>
+        <v>121448822</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4395,10 +4220,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437009</v>
+        <v>436909</v>
       </c>
       <c r="R36" t="n">
-        <v>6751557</v>
+        <v>6751837</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4255,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4440,7 +4265,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4470,16 +4295,11 @@
         <v>121448834</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4579,15 +4399,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121448783</v>
+        <v>118348346</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4595,34 +4410,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åsen, Åsen, Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437008</v>
+        <v>436906</v>
       </c>
       <c r="R38" t="n">
-        <v>6751526</v>
+        <v>6751733</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4649,22 +4464,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4691,55 +4496,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121448549</v>
+        <v>121448863</v>
       </c>
       <c r="B39" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437464</v>
+        <v>437149</v>
       </c>
       <c r="R39" t="n">
-        <v>6751755</v>
+        <v>6751833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4766,12 +4566,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4798,15 +4608,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121448543</v>
+        <v>118348347</v>
       </c>
       <c r="B40" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4838,10 +4643,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437495</v>
+        <v>437246</v>
       </c>
       <c r="R40" t="n">
-        <v>6751751</v>
+        <v>6751611</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4900,15 +4705,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121448841</v>
+        <v>121448543</v>
       </c>
       <c r="B41" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4916,34 +4716,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437073</v>
+        <v>437495</v>
       </c>
       <c r="R41" t="n">
-        <v>6751772</v>
+        <v>6751751</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4970,22 +4770,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5012,15 +4802,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121448548</v>
+        <v>121448816</v>
       </c>
       <c r="B42" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5028,34 +4813,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437511</v>
+        <v>436864</v>
       </c>
       <c r="R42" t="n">
-        <v>6751768</v>
+        <v>6751900</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5082,12 +4867,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5114,15 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121448832</v>
+        <v>121448843</v>
       </c>
       <c r="B43" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5130,39 +4920,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437014</v>
+        <v>437149</v>
       </c>
       <c r="R43" t="n">
-        <v>6751835</v>
+        <v>6751802</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5194,7 +4979,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5204,7 +4989,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5231,15 +5016,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121448868</v>
+        <v>121448871</v>
       </c>
       <c r="B44" t="n">
-        <v>78353</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5247,34 +5027,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437149</v>
+        <v>437372</v>
       </c>
       <c r="R44" t="n">
-        <v>6751833</v>
+        <v>6751643</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5306,7 +5086,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5316,7 +5096,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5343,15 +5123,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121448827</v>
+        <v>121448832</v>
       </c>
       <c r="B45" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5359,34 +5134,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åsen, Åsen, Dlr</t>
+          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436923</v>
+        <v>437014</v>
       </c>
       <c r="R45" t="n">
-        <v>6751806</v>
+        <v>6751835</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5418,7 +5198,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5428,7 +5208,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5455,50 +5235,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121448816</v>
+        <v>121448549</v>
       </c>
       <c r="B46" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Åsen, Åsen, Dlr</t>
+          <t>Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436864</v>
+        <v>437464</v>
       </c>
       <c r="R46" t="n">
-        <v>6751900</v>
+        <v>6751755</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5525,22 +5305,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5567,15 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121448546</v>
+        <v>111440954</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5583,37 +5348,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437496</v>
+        <v>437016</v>
       </c>
       <c r="R47" t="n">
-        <v>6751751</v>
+        <v>6751564</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5637,12 +5408,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5669,15 +5450,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121448544</v>
+        <v>121448819</v>
       </c>
       <c r="B48" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5685,34 +5461,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Åsen, Dlr</t>
+          <t>Åsen, Åsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437406</v>
+        <v>436864</v>
       </c>
       <c r="R48" t="n">
-        <v>6751644</v>
+        <v>6751900</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5739,12 +5515,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5771,15 +5557,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121448871</v>
+        <v>121448868</v>
       </c>
       <c r="B49" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5787,34 +5568,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Åsen, Åsen, Dlr</t>
+          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437372</v>
+        <v>437149</v>
       </c>
       <c r="R49" t="n">
-        <v>6751643</v>
+        <v>6751833</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5846,7 +5627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5856,7 +5637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5883,15 +5664,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121448839</v>
+        <v>111440236</v>
       </c>
       <c r="B50" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5917,19 +5693,20 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
+          <t>Oradtjärnen, Oradtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437059</v>
+        <v>436891</v>
       </c>
       <c r="R50" t="n">
-        <v>6751803</v>
+        <v>6751465</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5953,22 +5730,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5992,6 +5769,501 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118348348</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Åsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>436896</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6751461</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>118348349</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Åsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>436786</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6751885</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118348350</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Åsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>437350</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6751659</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121448544</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Åsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>437406</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6751644</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121448839</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stamsmyren, Venjan, Stamsmyren, Venjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>437059</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6751803</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48348-2024 artfynd.xlsx
+++ b/artfynd/A 48348-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111026118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111440239</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348358</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348359</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348360</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348361</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348362</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,6 +1514,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348363</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448548</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448841</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1786,6 +1841,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111441110</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1883,6 +1943,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348352</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1980,6 +2045,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448545</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2077,6 +2147,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448547</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348495</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2281,6 +2361,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348351</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2388,6 +2473,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448787</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2495,6 +2585,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448827</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2603,6 +2698,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111440259</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2711,6 +2811,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111440359</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2819,6 +2924,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111440369</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2927,6 +3037,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111440929</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3035,6 +3150,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111441133</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3132,6 +3252,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348354</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3229,6 +3354,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348355</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3326,6 +3456,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448546</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3433,6 +3568,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448724</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3540,6 +3680,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448783</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3647,6 +3792,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448790</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3754,6 +3904,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448792</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3861,6 +4016,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448794</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3968,6 +4128,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448795</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4075,6 +4240,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448800</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4182,6 +4352,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448809</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4289,6 +4464,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448822</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4396,6 +4576,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448834</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4493,6 +4678,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348346</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4605,6 +4795,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448863</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4702,6 +4897,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348347</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4799,6 +4999,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448543</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4906,6 +5111,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448816</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5013,6 +5223,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448843</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5120,6 +5335,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448871</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5232,6 +5452,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448832</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5334,6 +5559,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448549</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5447,6 +5677,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111440954</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5554,6 +5789,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448819</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5661,6 +5901,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448868</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5769,6 +6014,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111440236</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5866,6 +6116,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348348</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5963,6 +6218,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348349</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6060,6 +6320,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348350</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6157,6 +6422,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448544</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6264,8 +6534,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121448839</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>